--- a/income_expenses/static/income_expenses/template_old_data.xlsx
+++ b/income_expenses/static/income_expenses/template_old_data.xlsx
@@ -1,42 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TelisK\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TelisK\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A420012-7FDD-4FC3-8613-E48870BEF1AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69202793-F5A8-4D62-9F5B-114F9D38AE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10008" yWindow="828" windowWidth="8820" windowHeight="8880" xr2:uid="{949AEF00-D1E7-4073-A370-407B05891EC4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Έσοδα" sheetId="1" r:id="rId1"/>
+    <sheet name="Έξοδα" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t>store</t>
   </si>
@@ -61,18 +46,26 @@
   <si>
     <t>comments</t>
   </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <charset val="161"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -96,14 +89,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -126,44 +120,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -190,32 +184,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -242,24 +218,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -271,169 +229,181 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{999A234E-E33C-4168-87B9-31A7D8D7A887}">
-  <dimension ref="A1:H1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H214"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -461,7 +431,683 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B3" s="1"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="1"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="1"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="1"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="1"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="1"/>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B17" s="1"/>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B18" s="1"/>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B19" s="1"/>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B20" s="1"/>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B21" s="1"/>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B22" s="1"/>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B23" s="1"/>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B24" s="1"/>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B25" s="1"/>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B26" s="1"/>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B27" s="1"/>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B28" s="1"/>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B29" s="1"/>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B30" s="1"/>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B31" s="1"/>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B32" s="1"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B33" s="1"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B34" s="1"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B35" s="1"/>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B36" s="1"/>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B37" s="1"/>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B38" s="1"/>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B39" s="1"/>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B40" s="1"/>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B41" s="1"/>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B42" s="1"/>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B43" s="1"/>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B44" s="1"/>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B45" s="1"/>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B46" s="1"/>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B47" s="1"/>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B48" s="1"/>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B49" s="1"/>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B50" s="1"/>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B51" s="1"/>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B52" s="1"/>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B53" s="1"/>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B54" s="1"/>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B55" s="1"/>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B56" s="1"/>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B57" s="1"/>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B58" s="1"/>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B59" s="1"/>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B60" s="1"/>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B61" s="1"/>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B62" s="1"/>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B63" s="1"/>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B64" s="1"/>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B65" s="1"/>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B66" s="1"/>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B67" s="1"/>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B68" s="1"/>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B69" s="1"/>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B70" s="1"/>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B71" s="1"/>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B72" s="1"/>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B73" s="1"/>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B74" s="1"/>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B75" s="1"/>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B76" s="1"/>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B77" s="1"/>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B78" s="1"/>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B79" s="1"/>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B80" s="1"/>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B81" s="1"/>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B82" s="1"/>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B83" s="1"/>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B84" s="1"/>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B85" s="1"/>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B86" s="1"/>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B87" s="1"/>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B88" s="1"/>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B89" s="1"/>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B90" s="1"/>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B91" s="1"/>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B92" s="1"/>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B93" s="1"/>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B94" s="1"/>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B95" s="1"/>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B96" s="1"/>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B97" s="1"/>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B98" s="1"/>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B99" s="1"/>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B100" s="1"/>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B101" s="1"/>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B102" s="1"/>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B103" s="1"/>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B104" s="1"/>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B105" s="1"/>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B106" s="1"/>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B107" s="1"/>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B108" s="1"/>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B109" s="1"/>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B110" s="1"/>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B111" s="1"/>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B112" s="1"/>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B113" s="1"/>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B114" s="1"/>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B115" s="1"/>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B116" s="1"/>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B117" s="1"/>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B118" s="1"/>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B119" s="1"/>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B120" s="1"/>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B121" s="1"/>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B122" s="1"/>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B123" s="1"/>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B124" s="1"/>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B125" s="1"/>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B126" s="1"/>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B127" s="1"/>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B128" s="1"/>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B129" s="1"/>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B130" s="1"/>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B131" s="1"/>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B132" s="1"/>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B133" s="1"/>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B134" s="1"/>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B135" s="1"/>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B136" s="1"/>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B137" s="1"/>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B138" s="1"/>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B139" s="1"/>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B140" s="1"/>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B141" s="1"/>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B142" s="1"/>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B143" s="1"/>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B144" s="1"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B145" s="1"/>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B146" s="1"/>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B147" s="1"/>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B148" s="1"/>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B149" s="1"/>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B150" s="1"/>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B151" s="1"/>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B152" s="1"/>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B153" s="1"/>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B154" s="1"/>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B155" s="1"/>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B156" s="1"/>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B157" s="1"/>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B158" s="1"/>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B159" s="1"/>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B160" s="1"/>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B161" s="1"/>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B162" s="1"/>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B163" s="1"/>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B164" s="1"/>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B165" s="1"/>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B166" s="1"/>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B167" s="1"/>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B168" s="1"/>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B169" s="1"/>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B170" s="1"/>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B171" s="1"/>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B172" s="1"/>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B173" s="1"/>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B174" s="1"/>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B175" s="1"/>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B176" s="1"/>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B177" s="1"/>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B178" s="1"/>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B179" s="1"/>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B180" s="1"/>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B181" s="1"/>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B182" s="1"/>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B183" s="1"/>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B184" s="1"/>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B185" s="1"/>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B186" s="1"/>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B187" s="1"/>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B188" s="1"/>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B189" s="1"/>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B190" s="1"/>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B191" s="1"/>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B192" s="1"/>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B193" s="1"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B194" s="1"/>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B195" s="1"/>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B196" s="1"/>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B197" s="1"/>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B198" s="1"/>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B199" s="1"/>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B200" s="1"/>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B201" s="1"/>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B202" s="1"/>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B203" s="1"/>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B204" s="1"/>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B205" s="1"/>
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B206" s="1"/>
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B207" s="1"/>
+    </row>
+    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B208" s="1"/>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B209" s="1"/>
+    </row>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B210" s="1"/>
+    </row>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B211" s="1"/>
+    </row>
+    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B212" s="1"/>
+    </row>
+    <row r="213" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B213" s="1"/>
+    </row>
+    <row r="214" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B214" s="1"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.21875" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B3" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>